--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104592_W15.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104592_W15.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>M. HUGHES</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1738</v>
+        <v>2.3385</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7229</v>
+        <v>2.4791</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.5491</v>
+        <v>-0.1406</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2235</v>
+        <v>1.4543</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9942</v>
+        <v>0.9792</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2293</v>
+        <v>0.4751</v>
       </c>
       <c r="J2" t="n">
-        <v>2.7682</v>
+        <v>2.584</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4995</v>
+        <v>1.296</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2688</v>
+        <v>1.288</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.5447</v>
+        <v>-1.1296</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5053</v>
+        <v>-0.3168</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.0395</v>
+        <v>-0.8129</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5878</v>
+        <v>0.6829</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.4537</v>
+        <v>-1.5934</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0415</v>
+        <v>2.2763</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9088000000000001</v>
+        <v>-0.1857</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3157</v>
+        <v>0.2413</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4068</v>
+        <v>-0.427</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.5463</v>
+        <v>0.387</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.2472</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.639</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. HUGHES</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4192</v>
+        <v>1.8553</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5977</v>
+        <v>3.5248</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1786</v>
+        <v>-1.6695</v>
       </c>
       <c r="G3" t="n">
-        <v>1.454</v>
+        <v>1.2352</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9768</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4771</v>
+        <v>0.2388</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6096</v>
+        <v>2.7517</v>
       </c>
       <c r="K3" t="n">
-        <v>1.309</v>
+        <v>1.4856</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3007</v>
+        <v>1.2661</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1557</v>
+        <v>-1.5164</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3321</v>
+        <v>-0.4891</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8236</v>
+        <v>-1.0273</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6805</v>
+        <v>1.5934</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.5878</v>
+        <v>-0.4553</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2683</v>
+        <v>2.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1009</v>
+        <v>-0.4286</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6775</v>
+        <v>0.1389</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4234</v>
+        <v>-0.5675</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3856</v>
+        <v>-0.5447</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2534</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8678</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. MARIC</t>
+          <t>S. MARTINEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3487</v>
+        <v>0.2206</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6644</v>
+        <v>1.3579</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0131</v>
+        <v>-1.1373</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.3197</v>
+        <v>-1.0513</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3895</v>
+        <v>0.758</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9302</v>
+        <v>-1.8093</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2492</v>
+        <v>1.969</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0999</v>
+        <v>1.2615</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1493</v>
+        <v>0.7075</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5689</v>
+        <v>-3.0203</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4894</v>
+        <v>-0.5036</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0795</v>
+        <v>-2.5168</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.361</v>
+        <v>-1.5934</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5878</v>
+        <v>2.5039</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9049</v>
+        <v>-0.7281</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4548</v>
+        <v>-0.1072</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5498</v>
+        <v>-0.6209</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3214</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.4822</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. MARTINEZ</t>
+          <t>P. VILDOZA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.548</v>
+        <v>-0.3783</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5325</v>
+        <v>-0.0059</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0805</v>
+        <v>-0.3723</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.07</v>
+        <v>-0.2189</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7531</v>
+        <v>-0.4975</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.8231</v>
+        <v>0.2786</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9834</v>
+        <v>0.0385</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2743</v>
+        <v>0.1207</v>
       </c>
       <c r="L5" t="n">
-        <v>0.709</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.0533</v>
+        <v>-0.2574</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5212</v>
+        <v>-0.6182</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.5321</v>
+        <v>0.3608</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.5878</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4952</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.478</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9557</v>
+        <v>-0.1535</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5223</v>
+        <v>0.1535</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0927</v>
+        <v>-0.387</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>1.2472</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. VILDOZA</t>
+          <t>N. MARIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0577</v>
+        <v>-1.2031</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5325</v>
+        <v>-0.4746</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5252</v>
+        <v>-0.7285</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2323</v>
+        <v>-1.3192</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.396</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2772</v>
+        <v>-0.9233</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0439</v>
+        <v>0.2277</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1212</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.07729999999999999</v>
+        <v>0.1489</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2762</v>
+        <v>-1.5469</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6308</v>
+        <v>-0.4747</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3546</v>
+        <v>-1.0722</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="R6" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6666</v>
+        <v>0.0463</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6956</v>
+        <v>0.348</v>
       </c>
       <c r="U6" t="n">
-        <v>0.029</v>
+        <v>-0.3017</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3856</v>
+        <v>-0.1578</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2534</v>
+        <v>0.3155</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.639</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="7">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5405</v>
+        <v>-1.2891</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2111</v>
+        <v>-0.8874</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3294</v>
+        <v>-0.4017</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4632</v>
+        <v>-1.4689</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.1802</v>
+        <v>-2.1854</v>
       </c>
       <c r="I7" t="n">
-        <v>0.717</v>
+        <v>0.7165</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3884</v>
+        <v>0.365</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.2508</v>
+        <v>-1.2658</v>
       </c>
       <c r="L7" t="n">
-        <v>1.6392</v>
+        <v>1.6308</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.8516</v>
+        <v>-1.8339</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9294</v>
+        <v>-0.9196</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4649</v>
+        <v>-0.2056</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6261</v>
+        <v>-0.272</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1612</v>
+        <v>0.0664</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. GEBEN</t>
+          <t>M. SUSINSKAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0539</v>
+        <v>-2.2255</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1018</v>
+        <v>-2.1247</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.952</v>
+        <v>-0.1007</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.5294</v>
+        <v>-3.5984</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.8742</v>
+        <v>0.287</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6552</v>
+        <v>-3.8853</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.1228</v>
+        <v>-2.2223</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.4484</v>
+        <v>0.8618</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6744</v>
+        <v>-3.0841</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4066</v>
+        <v>-1.3761</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4258</v>
+        <v>-0.5749</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9808</v>
+        <v>-0.8012</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6805</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0634</v>
+        <v>0.2834</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1039</v>
+        <v>0.1462</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0405</v>
+        <v>0.1372</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W8" t="n">
-        <v>2.1853</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4374</v>
+        <v>-2.2936</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5274</v>
+        <v>-2.6063</v>
       </c>
       <c r="F9" t="n">
-        <v>0.09</v>
+        <v>0.3126</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3509</v>
+        <v>-1.3466</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4457</v>
+        <v>0.4561</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.7966</v>
+        <v>-1.8027</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5952</v>
+        <v>-0.617</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2814</v>
+        <v>1.2755</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.8767</v>
+        <v>-1.8925</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7557</v>
+        <v>-0.7296</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8357</v>
+        <v>-0.8194</v>
       </c>
       <c r="O9" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4494</v>
+        <v>-0.3112</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0393</v>
+        <v>-0.0073</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4888</v>
+        <v>-0.3039</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.3176</v>
+        <v>-1.3187</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. SUSINSKAS</t>
+          <t>M. GEBEN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5923</v>
+        <v>-2.506</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6638</v>
+        <v>-1.706</v>
       </c>
       <c r="F10" t="n">
-        <v>0.07149999999999999</v>
+        <v>-0.7999000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.593</v>
+        <v>-3.535</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2828</v>
+        <v>-1.8863</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.8758</v>
+        <v>-1.6487</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.205</v>
+        <v>-2.1473</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8658</v>
+        <v>-1.4694</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.0708</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.388</v>
+        <v>-1.3877</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5831</v>
+        <v>-0.4169</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.805</v>
+        <v>-0.9708</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0919</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4174</v>
+        <v>0.5386</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3254</v>
+        <v>0.0838</v>
       </c>
       <c r="V10" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0927</v>
+        <v>2.1789</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4097</v>
+        <v>-3.8675</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8266</v>
+        <v>-1.1651</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.5831</v>
+        <v>-2.7024</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.4593</v>
+        <v>-3.4809</v>
       </c>
       <c r="H11" t="n">
-        <v>0.635</v>
+        <v>0.6266</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.0944</v>
+        <v>-4.1075</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2646</v>
+        <v>-0.317</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9831</v>
+        <v>0.9578</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2477</v>
+        <v>-1.2748</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.1947</v>
+        <v>-3.1638</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.348</v>
+        <v>-0.3312</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.8467</v>
+        <v>-2.8326</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5893</v>
+        <v>-1.0208</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0253</v>
+        <v>-0.2954</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5641</v>
+        <v>-0.7254</v>
       </c>
       <c r="V11" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W11" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.3952</v>
+        <v>-9.348700000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3457</v>
+        <v>-1.6082</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.0495</v>
+        <v>-7.7403</v>
       </c>
       <c r="G12" t="n">
-        <v>-13.3403</v>
+        <v>-13.3297</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8658999999999997</v>
+        <v>-0.8617999999999997</v>
       </c>
       <c r="I12" t="n">
-        <v>-12.4747</v>
+        <v>-12.4678</v>
       </c>
       <c r="J12" t="n">
-        <v>2.8551</v>
+        <v>2.6323</v>
       </c>
       <c r="K12" t="n">
-        <v>4.735000000000001</v>
+        <v>4.6024</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.879900000000001</v>
+        <v>-1.970099999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-16.1954</v>
+        <v>-15.9617</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.6008</v>
+        <v>-5.464399999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-10.5948</v>
+        <v>-10.4975</v>
       </c>
       <c r="P12" t="n">
-        <v>3.4023</v>
+        <v>3.414299999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-14.7442</v>
+        <v>-14.7962</v>
       </c>
       <c r="R12" t="n">
-        <v>18.1466</v>
+        <v>18.2105</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.9639</v>
+        <v>-1.9278</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4838999999999996</v>
+        <v>0.5775999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.480099999999999</v>
+        <v>-2.5055</v>
       </c>
       <c r="V12" t="n">
-        <v>2.5069</v>
+        <v>2.4946</v>
       </c>
       <c r="W12" t="n">
-        <v>10.0271</v>
+        <v>9.9778</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.520499999999999</v>
+        <v>-7.4835</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>T. FORREST</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.7106</v>
+        <v>4.8236</v>
       </c>
       <c r="E13" t="n">
-        <v>8.359</v>
+        <v>4.8889</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.6485</v>
+        <v>-0.0654</v>
       </c>
       <c r="G13" t="n">
-        <v>4.3672</v>
+        <v>6.7458</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4329</v>
+        <v>3.071</v>
       </c>
       <c r="I13" t="n">
-        <v>3.9343</v>
+        <v>3.6748</v>
       </c>
       <c r="J13" t="n">
-        <v>4.8116</v>
+        <v>7.5884</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8587</v>
+        <v>3.5745</v>
       </c>
       <c r="L13" t="n">
-        <v>3.9529</v>
+        <v>4.0139</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4444</v>
+        <v>-0.8426</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4258</v>
+        <v>-0.5036</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0186</v>
+        <v>-0.3391</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.2268</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9073</v>
+        <v>-3.8697</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6805</v>
+        <v>2.0487</v>
       </c>
       <c r="S13" t="n">
-        <v>3.6629</v>
+        <v>-0.2589</v>
       </c>
       <c r="T13" t="n">
-        <v>2.8158</v>
+        <v>-0.077</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8471</v>
+        <v>-0.1819</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="W13" t="n">
-        <v>1.639</v>
+        <v>1.2472</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.7317</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T. FORREST</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6457</v>
+        <v>4.5967</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1254</v>
+        <v>6.5629</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4797</v>
+        <v>-1.9662</v>
       </c>
       <c r="G14" t="n">
-        <v>6.7596</v>
+        <v>4.3588</v>
       </c>
       <c r="H14" t="n">
-        <v>3.0838</v>
+        <v>0.4309</v>
       </c>
       <c r="I14" t="n">
-        <v>3.6758</v>
+        <v>3.9278</v>
       </c>
       <c r="J14" t="n">
-        <v>7.6325</v>
+        <v>4.7873</v>
       </c>
       <c r="K14" t="n">
-        <v>3.605</v>
+        <v>0.8479</v>
       </c>
       <c r="L14" t="n">
-        <v>4.0275</v>
+        <v>3.9394</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8729</v>
+        <v>-0.4285</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5212</v>
+        <v>-0.4169</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3517</v>
+        <v>-0.0116</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.8147</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.8562</v>
+        <v>-0.9105</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0415</v>
+        <v>0.6829</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.4599</v>
+        <v>1.555</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9043</v>
+        <v>1.0519</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5556</v>
+        <v>0.5032</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1607</v>
+        <v>-1.0895</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2534</v>
+        <v>1.6342</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0927</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="15">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5338</v>
+        <v>3.5737</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5971</v>
+        <v>2.5845</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9367</v>
+        <v>0.9892</v>
       </c>
       <c r="G15" t="n">
-        <v>2.291</v>
+        <v>2.295</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1182</v>
+        <v>1.1227</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1728</v>
+        <v>1.1723</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5941</v>
+        <v>2.5801</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4027</v>
+        <v>1.3962</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1914</v>
+        <v>1.1839</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.303</v>
+        <v>-0.2851</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2844</v>
+        <v>-0.2734</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3354</v>
+        <v>0.3681</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4567</v>
+        <v>0.4596</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1213</v>
+        <v>-0.0915</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4559</v>
+        <v>2.7407</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9316</v>
+        <v>0.6207</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5243</v>
+        <v>2.12</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5534</v>
+        <v>0.7959000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4804</v>
+        <v>0.218</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.0338</v>
+        <v>0.5778</v>
       </c>
       <c r="J16" t="n">
-        <v>0.096</v>
+        <v>1.0517</v>
       </c>
       <c r="K16" t="n">
-        <v>2.2685</v>
+        <v>1.0375</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.1725</v>
+        <v>0.0142</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6494</v>
+        <v>-0.2558</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.788</v>
+        <v>-0.8194</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1387</v>
+        <v>0.5636</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.361</v>
+        <v>-2.9592</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5878</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>1.24</v>
+        <v>0.1301</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1039</v>
+        <v>-0.1955</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1361</v>
+        <v>0.3256</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5425</v>
+        <v>2.9529</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>2.7237</v>
       </c>
       <c r="X16" t="n">
-        <v>0.4498</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.882</v>
+        <v>2.0316</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.043</v>
+        <v>0.3166</v>
       </c>
       <c r="F17" t="n">
-        <v>1.925</v>
+        <v>1.715</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7945</v>
+        <v>-0.5545</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2135</v>
+        <v>1.4819</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5810999999999999</v>
+        <v>-2.0364</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0784</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0492</v>
+        <v>2.258</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0292</v>
+        <v>-2.1827</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2839</v>
+        <v>-0.6298</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8357</v>
+        <v>-0.7761</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.1463</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1342</v>
+        <v>0.2276</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9488</v>
+        <v>-1.3658</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8147</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7349</v>
+        <v>0.8106</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9043</v>
+        <v>0.5177</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1693</v>
+        <v>0.2929</v>
       </c>
       <c r="V17" t="n">
-        <v>2.9566</v>
+        <v>1.5479</v>
       </c>
       <c r="W17" t="n">
-        <v>2.7317</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>0.2249</v>
+        <v>0.4584</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8762</v>
+        <v>1.1834</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0458</v>
+        <v>0.2608</v>
       </c>
       <c r="F18" t="n">
-        <v>0.922</v>
+        <v>0.9227</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2539</v>
+        <v>1.2389</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.5178</v>
+        <v>-2.5297</v>
       </c>
       <c r="I18" t="n">
-        <v>3.7717</v>
+        <v>3.7686</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4474</v>
+        <v>1.4094</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.8711</v>
+        <v>-1.897</v>
       </c>
       <c r="L18" t="n">
-        <v>3.3185</v>
+        <v>3.3064</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1935</v>
+        <v>-0.1704</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4532</v>
+        <v>0.4622</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0305</v>
+        <v>0.3542</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0907</v>
+        <v>0.448</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0602</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.5425</v>
+        <v>-1.5479</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.4498</v>
+        <v>-0.4584</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3212</v>
+        <v>0.8483000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7735</v>
+        <v>-0.0984</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0947</v>
+        <v>0.9467</v>
       </c>
       <c r="G19" t="n">
-        <v>1.4131</v>
+        <v>1.4187</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4444</v>
+        <v>-1.4446</v>
       </c>
       <c r="I19" t="n">
-        <v>2.8575</v>
+        <v>2.8633</v>
       </c>
       <c r="J19" t="n">
-        <v>1.497</v>
+        <v>1.4745</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5928</v>
+        <v>-0.6108</v>
       </c>
       <c r="L19" t="n">
-        <v>2.0897</v>
+        <v>2.0853</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0839</v>
+        <v>-0.0558</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8516</v>
+        <v>-0.8339</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7678</v>
+        <v>0.778</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8154</v>
+        <v>1.3402</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0393</v>
+        <v>0.7521</v>
       </c>
       <c r="U19" t="n">
-        <v>0.776</v>
+        <v>0.5881</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.9839</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0518</v>
+        <v>-1.7678</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9799</v>
+        <v>0.7839</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6993</v>
+        <v>-0.6901</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0245</v>
+        <v>-1.0226</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3253</v>
+        <v>0.3325</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2303</v>
+        <v>-1.238</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.4169</v>
+        <v>-1.4242</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="M20" t="n">
-        <v>0.531</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3923</v>
+        <v>0.4016</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S20" t="n">
-        <v>1.4932</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0858</v>
+        <v>0.3807</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4074</v>
+        <v>0.1873</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3191</v>
+        <v>-1.2518</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0522</v>
+        <v>-0.0525</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2668</v>
+        <v>-1.1994</v>
       </c>
       <c r="G21" t="n">
-        <v>0.116</v>
+        <v>0.1187</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1746</v>
+        <v>0.1752</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2092,22 +2092,22 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3424</v>
+        <v>-0.281</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2728</v>
+        <v>-0.2113</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0949</v>
+        <v>-2.9063</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5148</v>
+        <v>-2.5312</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.3752</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0527</v>
+        <v>-1.0495</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4054</v>
+        <v>0.4104</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.4581</v>
+        <v>-1.4599</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6669</v>
+        <v>-0.6774</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8312</v>
+        <v>0.8274</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.4981</v>
+        <v>-1.5048</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3858</v>
+        <v>-0.372</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4258</v>
+        <v>-0.4169</v>
       </c>
       <c r="O22" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7473</v>
+        <v>-0.5609</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4869</v>
+        <v>-0.4879</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2604</v>
+        <v>-0.073</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.5443</v>
+        <v>-3.4724</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4825</v>
+        <v>-3.0443</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0618</v>
+        <v>-0.428</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3496</v>
+        <v>-1.348</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.0563</v>
+        <v>-1.0514</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2932</v>
+        <v>-0.2966</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.0816</v>
+        <v>-1.1066</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.551</v>
+        <v>-0.5623</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5306</v>
+        <v>-0.5443</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.268</v>
+        <v>-0.2414</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5053</v>
+        <v>-0.4891</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2373</v>
+        <v>0.2477</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3289</v>
+        <v>-0.2625</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.747</v>
+        <v>-0.2744</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5819</v>
+        <v>0.0119</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>10.3951</v>
+        <v>11.1836</v>
       </c>
       <c r="E24" t="n">
-        <v>8.049500000000004</v>
+        <v>7.740199999999998</v>
       </c>
       <c r="F24" t="n">
-        <v>2.3457</v>
+        <v>3.4433</v>
       </c>
       <c r="G24" t="n">
-        <v>13.3403</v>
+        <v>13.3297</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8658000000000012</v>
+        <v>0.8617999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>12.4748</v>
+        <v>12.4677</v>
       </c>
       <c r="J24" t="n">
-        <v>16.1955</v>
+        <v>15.9619</v>
       </c>
       <c r="K24" t="n">
-        <v>5.6008</v>
+        <v>5.464399999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>10.5946</v>
+        <v>10.4975</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.8552</v>
+        <v>-2.6321</v>
       </c>
       <c r="N24" t="n">
-        <v>-4.7349</v>
+        <v>-4.602399999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>1.8801</v>
+        <v>1.9702</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.4026</v>
+        <v>-3.414599999999999</v>
       </c>
       <c r="Q24" t="n">
-        <v>-18.1467</v>
+        <v>-18.2106</v>
       </c>
       <c r="R24" t="n">
-        <v>14.7441</v>
+        <v>14.7961</v>
       </c>
       <c r="S24" t="n">
-        <v>2.964</v>
+        <v>3.7629</v>
       </c>
       <c r="T24" t="n">
-        <v>2.4801</v>
+        <v>2.505500000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4837000000000001</v>
+        <v>1.2576</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.5068</v>
+        <v>-2.494499999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>7.5204</v>
+        <v>7.4835</v>
       </c>
       <c r="X24" t="n">
-        <v>-10.0272</v>
+        <v>-9.9781</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104592_W15.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104592_W15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104592_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104592_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104592_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104592_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104592_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104592_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104592_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104592_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104592_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104592_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-7.4835</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104592_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104592_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104592_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104592_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.4584</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104592_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104592_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104592_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104592_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104592_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104592_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104592_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-9.9781</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
